--- a/models/llmtypes.xlsx
+++ b/models/llmtypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4D07E7-04EC-EB44-99D3-CD4F16968DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81ED14FF-8609-3E4A-A80E-002FB8FE2C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34220" yWindow="10800" windowWidth="28800" windowHeight="19480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="23400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -240,9 +240,6 @@
     <t>cond</t>
   </si>
   <si>
-    <t>modeltype</t>
-  </si>
-  <si>
     <t>模型类型</t>
   </si>
   <si>
@@ -304,6 +301,10 @@
   <si>
     <t>text</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>modeltypes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -731,10 +732,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
@@ -812,10 +813,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -826,10 +827,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -840,10 +841,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -1032,45 +1033,45 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="E2" s="8"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>84</v>
-      </c>
       <c r="C3" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>86</v>
-      </c>
       <c r="C4" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1202,7 +1203,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
